--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q4_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.01_Q4_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0009299470567550967</v>
+        <v>0.0002259836570879022</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009299470567550967</v>
+        <v>0.0002259836570879022</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0009130865766844002</v>
+        <v>0.0002221671498809487</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009130865766844002</v>
+        <v>0.0002221671498809487</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0009149245490673244</v>
+        <v>0.0002224927411292459</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009149245490673244</v>
+        <v>0.0002224927411292459</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0009146496780075723</v>
+        <v>0.0002221006630648485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009146496780075723</v>
+        <v>0.0002221006630648485</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0009066192884140114</v>
+        <v>0.000219719259764724</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009066192884140114</v>
+        <v>0.000219719259764724</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0009005780001982703</v>
+        <v>0.0002177572016970621</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009005780001982703</v>
+        <v>0.0002177572016970621</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0008891849723301949</v>
+        <v>0.0002144884749017356</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0008891849723301949</v>
+        <v>0.0002144884749017356</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0008767489460005011</v>
+        <v>0.0002109432685941688</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0008767489460005011</v>
+        <v>0.0002109432685941688</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0008635209830282724</v>
+        <v>0.0002072210417183495</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008635209830282724</v>
+        <v>0.0002072210417183495</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0008501300251482049</v>
+        <v>0.0002035016747855853</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0008501300251482049</v>
+        <v>0.0002035016747855853</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0008372305017138403</v>
+        <v>0.0001999568166670585</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0008372305017138403</v>
+        <v>0.0001999568166670585</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.000825485892167453</v>
+        <v>0.0001967609484788566</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000825485892167453</v>
+        <v>0.0001967609484788566</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0008153117085339682</v>
+        <v>0.000194019568856795</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0008153117085339682</v>
+        <v>0.000194019568856795</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0008068815837857016</v>
+        <v>0.0001917745601843257</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0008068815837857016</v>
+        <v>0.0001917745601843257</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0008002822402324714</v>
+        <v>0.0001900443717848146</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0008002822402324714</v>
+        <v>0.0001900443717848146</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0007956476879328617</v>
+        <v>0.0001888583225476255</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0007956476879328617</v>
+        <v>0.0001888583225476255</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0007932340041930722</v>
+        <v>0.0001882756156564302</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0007932340041930722</v>
+        <v>0.0001882756156564302</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0007933597206763002</v>
+        <v>0.0001883702457239324</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0007933597206763002</v>
+        <v>0.0001883702457239324</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0007963410494067888</v>
+        <v>0.0001892154197968887</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0007963410494067888</v>
+        <v>0.0001892154197968887</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0008024372801237491</v>
+        <v>0.0001908697856800774</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008024372801237491</v>
+        <v>0.0001908697856800774</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0008117907809313172</v>
+        <v>0.0001933616912636137</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0008117907809313172</v>
+        <v>0.0001933616912636137</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0008246670436156046</v>
+        <v>0.0001967543710107003</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0008246670436156046</v>
+        <v>0.0001967543710107003</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0008391236001360487</v>
+        <v>0.0002005704966032994</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0008391236001360487</v>
+        <v>0.0002005704966032994</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0008587470296411095</v>
+        <v>0.0002056715414418822</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0008587470296411095</v>
+        <v>0.0002056715414418822</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0008824007901338731</v>
+        <v>0.0002117864452798633</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0008824007901338731</v>
+        <v>0.0002117864452798633</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0009103321952588165</v>
+        <v>0.0002189676165890653</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0009103321952588165</v>
+        <v>0.0002189676165890653</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0009427233265480607</v>
+        <v>0.0002272601051758463</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0009427233265480607</v>
+        <v>0.0002272601051758463</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0009796586081088914</v>
+        <v>0.0002366798064522562</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0009796586081088914</v>
+        <v>0.0002366798064522562</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.001021191594577486</v>
+        <v>0.00024723781608867</v>
       </c>
       <c r="C30" t="n">
-        <v>0.001021191594577486</v>
+        <v>0.00024723781608867</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.001067429339514513</v>
+        <v>0.0002589580905133092</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001067429339514513</v>
+        <v>0.0002589580905133092</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
